--- a/01_formatos.xlsx
+++ b/01_formatos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulisesgtgm\Documents\Github\Repositories\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF30B46F-BA54-4C7D-83EE-6CB5BB291ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C32F668-0911-4DF4-9FBF-3932E74C9CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3218B744-8084-4331-8893-46E19DB1815D}"/>
   </bookViews>
@@ -35,8 +35,26 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>Genral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texto </t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="00000"/>
+    <numFmt numFmtId="166" formatCode="mm/dd/yy;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -66,8 +84,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +422,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4A191A-54F7-4C71-9B5D-569BA74A4E8B}">
-  <dimension ref="A1"/>
+  <dimension ref="B3:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46072</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/01_formatos.xlsx
+++ b/01_formatos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulisesgtgm\Documents\Github\Repositories\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C32F668-0911-4DF4-9FBF-3932E74C9CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739A610F-A5E2-4489-997B-29FF5F639FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3218B744-8084-4331-8893-46E19DB1815D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Genral</t>
   </si>
@@ -46,14 +46,21 @@
   <si>
     <t>Fecha</t>
   </si>
+  <si>
+    <t>Moneda</t>
+  </si>
+  <si>
+    <t>condicional</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="00000"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="166" formatCode="[$$-80A]#,##0.00"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -84,15 +91,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -422,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4A191A-54F7-4C71-9B5D-569BA74A4E8B}">
-  <dimension ref="B3:C5"/>
+  <dimension ref="B3:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
@@ -449,7 +465,29 @@
         <v>46072</v>
       </c>
     </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="C7">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>